--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513656_FASEFINALAFFA2_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513656_FASEFINALAFFA2_PROCESSED.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4849</v>
+        <v>2.9448</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5759</v>
+        <v>2.0636</v>
       </c>
       <c r="F2" t="n">
-        <v>0.909</v>
+        <v>0.8812</v>
       </c>
       <c r="G2" t="n">
         <v>2.8666</v>
@@ -610,13 +610,13 @@
         <v>1.1684</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6183</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0305</v>
+        <v>-0.4817</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5878</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. ARTECHE URRUZOLA</t>
+          <t>E. MARTINEZ CENDON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7142</v>
+        <v>2.1058</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.8277</v>
+        <v>-1.0942</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5419</v>
+        <v>3.1999</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4446</v>
+        <v>0.0123</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4255</v>
+        <v>0.4157</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0191</v>
+        <v>-0.4035</v>
       </c>
       <c r="J3" t="n">
-        <v>0.522</v>
+        <v>-1.3696</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4004</v>
+        <v>0.0643</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1216</v>
+        <v>-1.4339</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9226</v>
+        <v>1.3818</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0251</v>
+        <v>0.3514</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8975</v>
+        <v>1.0304</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9737</v>
+        <v>0.7789</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.1158</v>
+        <v>-1.1684</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1421</v>
+        <v>1.9474</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8023</v>
+        <v>-0.7965</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7661</v>
+        <v>-0.6673</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0362</v>
+        <v>-0.1292</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5590000000000001</v>
+        <v>2.1111</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.1111</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5590000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. MARTINEZ CENDON</t>
+          <t>P. ELOLA AGUIRREZABALA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5456</v>
+        <v>1.4104</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.6544</v>
+        <v>0.7323</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1999</v>
+        <v>0.6781</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0123</v>
+        <v>1.2987</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4157</v>
+        <v>1.0329</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4035</v>
+        <v>0.2658</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.3696</v>
+        <v>0.7184</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0643</v>
+        <v>0.7184</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.4339</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.3818</v>
+        <v>0.5803</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3514</v>
+        <v>0.3145</v>
       </c>
       <c r="O4" t="n">
-        <v>1.0304</v>
+        <v>0.2658</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7789</v>
+        <v>0.3895</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1684</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9474</v>
+        <v>0.3895</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3567</v>
+        <v>0.0016</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2275</v>
+        <v>0.0138</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1292</v>
+        <v>-0.0122</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1111</v>
+        <v>-0.2795</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1111</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. ELOLA AGUIRREZABALA</t>
+          <t>M. ZUBIZARRETA ALBIZU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2388</v>
+        <v>1.0001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5329</v>
+        <v>0.2038</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7059</v>
+        <v>0.7964</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2987</v>
+        <v>0.5071</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0329</v>
+        <v>-0.4203</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2658</v>
+        <v>0.9273</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7184</v>
+        <v>0.5609</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7184</v>
+        <v>0.0257</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.5352</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5803</v>
+        <v>-0.0539</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3145</v>
+        <v>-0.446</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2658</v>
+        <v>0.3921</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3895</v>
+        <v>0.7789</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3895</v>
+        <v>0.7789</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1699</v>
+        <v>-0.2859</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1855</v>
+        <v>-0.3572</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0156</v>
+        <v>0.0713</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. ZUBIZARRETA ALBIZU</t>
+          <t>I. ARTECHE URRUZOLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.538</v>
+        <v>0.3905</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1193</v>
+        <v>-2.5393</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6572</v>
+        <v>2.9298</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5071</v>
+        <v>1.4446</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4203</v>
+        <v>0.4255</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9273</v>
+        <v>1.0191</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5609</v>
+        <v>0.522</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0257</v>
+        <v>0.4004</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5352</v>
+        <v>0.1216</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0539</v>
+        <v>0.9226</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.446</v>
+        <v>0.0251</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3921</v>
+        <v>0.8975</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7789</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.1158</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7789</v>
+        <v>2.1421</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.748</v>
+        <v>0.4785</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6802</v>
+        <v>0.0545</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0678</v>
+        <v>0.4241</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. SAGASTI ARGOTE</t>
+          <t>X. OSTOLAZA OSTOLAZA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7678</v>
+        <v>-0.6292</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4805</v>
+        <v>-1.54</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2873</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7495</v>
+        <v>-0.2529</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.08309999999999999</v>
+        <v>0.4182</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6663</v>
+        <v>-0.6711</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1864</v>
+        <v>-0.295</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0616</v>
+        <v>0.3695</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.248</v>
+        <v>-0.6645</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5631</v>
+        <v>0.0422</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1447</v>
+        <v>0.0487</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4184</v>
+        <v>-0.0066</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7789</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R8" t="n">
         <v>0.7789</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4822</v>
+        <v>-0.1816</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4264</v>
+        <v>-0.2713</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0558</v>
+        <v>0.0897</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5590000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X. OSTOLAZA OSTOLAZA</t>
+          <t>J. EGAA AYERZA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8804</v>
+        <v>-0.7266</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7634</v>
+        <v>-1.1367</v>
       </c>
       <c r="F9" t="n">
-        <v>0.883</v>
+        <v>0.4101</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2529</v>
+        <v>0.9433</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4182</v>
+        <v>-0.8005</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6711</v>
+        <v>1.7438</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.295</v>
+        <v>0.226</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3695</v>
+        <v>-0.4874</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6645</v>
+        <v>0.7134</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0422</v>
+        <v>0.7173</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0487</v>
+        <v>-0.3131</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0066</v>
+        <v>1.0304</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1947</v>
+        <v>0.3895</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9737</v>
+        <v>-1.1684</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7789</v>
+        <v>1.5579</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4328</v>
+        <v>-0.8383</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4947</v>
+        <v>-0.8048</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0619</v>
+        <v>-0.0335</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.6105</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. EGAA AYERZA</t>
+          <t>I. SAGASTI ARGOTE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0596</v>
+        <v>-1.1063</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4976</v>
+        <v>-0.6798999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>0.438</v>
+        <v>-0.4264</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9433</v>
+        <v>-1.7495</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8005</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7438</v>
+        <v>-1.6663</v>
       </c>
       <c r="J10" t="n">
-        <v>0.226</v>
+        <v>-1.1864</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4874</v>
+        <v>0.0616</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7134</v>
+        <v>-1.248</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7173</v>
+        <v>-0.5631</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3131</v>
+        <v>-0.1447</v>
       </c>
       <c r="O10" t="n">
-        <v>1.0304</v>
+        <v>-0.4184</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3895</v>
+        <v>0.7789</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1684</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5579</v>
+        <v>0.7789</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1713</v>
+        <v>0.1437</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1656</v>
+        <v>0.227</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0057</v>
+        <v>-0.0833</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2211</v>
+        <v>-0.2795</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6105</v>
+        <v>0.2795</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8316</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7419</v>
+        <v>-1.6028</v>
       </c>
       <c r="E11" t="n">
         <v>-0.8715000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8704</v>
+        <v>-0.7313</v>
       </c>
       <c r="G11" t="n">
         <v>1.0669</v>
@@ -1312,13 +1312,13 @@
         <v>0.1947</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7573</v>
+        <v>-0.6181</v>
       </c>
       <c r="T11" t="n">
         <v>-0.5565</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2007</v>
+        <v>-0.0616</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2726</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. LARRANAGA ORMAZABAL</t>
+          <t>E. ANDRES CAMPOS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0879</v>
+        <v>-3.3788</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0037</v>
+        <v>-5.6371</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0842</v>
+        <v>2.2583</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.0524</v>
+        <v>-0.0239</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3813</v>
+        <v>0.3587</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6711</v>
+        <v>-0.3826</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-1.1518</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0411</v>
+        <v>0.1284</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6645</v>
+        <v>-1.2801</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4289</v>
+        <v>1.1278</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4224</v>
+        <v>0.2303</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0066</v>
+        <v>0.8975</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.5579</v>
+        <v>-3.5053</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9474</v>
+        <v>-5.0631</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3895</v>
+        <v>1.5579</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2566</v>
+        <v>-0.7912</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4328</v>
+        <v>-0.6433</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1763</v>
+        <v>-0.1479</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2211</v>
+        <v>0.9416</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2211</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. ANDRES CAMPOS</t>
+          <t>M. LARRANAGA ORMAZABAL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.368</v>
+        <v>-3.8645</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.0977</v>
+        <v>-2.7803</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7296</v>
+        <v>-1.0842</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0239</v>
+        <v>-1.0524</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3587</v>
+        <v>-0.3813</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3826</v>
+        <v>-0.6711</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.1518</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1284</v>
+        <v>0.0411</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.2801</v>
+        <v>-0.6645</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1278</v>
+        <v>-0.4289</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2303</v>
+        <v>-0.4224</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8975</v>
+        <v>-0.0066</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.5053</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.0631</v>
+        <v>-1.9474</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5579</v>
+        <v>0.3895</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.7804</v>
+        <v>-0.0332</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1038</v>
+        <v>-0.2095</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6766</v>
+        <v>0.1763</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9416</v>
+        <v>-1.2211</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2211</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2795</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="14">
@@ -1501,37 +1501,37 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.076200000000002</v>
+        <v>-3.148700000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-13.8991</v>
+        <v>-12.9714</v>
       </c>
       <c r="F14" t="n">
-        <v>9.8226</v>
+        <v>9.822700000000001</v>
       </c>
       <c r="G14" t="n">
         <v>5.3687</v>
       </c>
       <c r="H14" t="n">
-        <v>4.769799999999999</v>
+        <v>4.7698</v>
       </c>
       <c r="I14" t="n">
         <v>0.5989</v>
       </c>
       <c r="J14" t="n">
-        <v>0.301300000000001</v>
+        <v>0.3013000000000005</v>
       </c>
       <c r="K14" t="n">
-        <v>5.486399999999999</v>
+        <v>5.4864</v>
       </c>
       <c r="L14" t="n">
-        <v>-5.1849</v>
+        <v>-5.184900000000001</v>
       </c>
       <c r="M14" t="n">
         <v>5.0672</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7166000000000001</v>
+        <v>-0.7165999999999999</v>
       </c>
       <c r="O14" t="n">
         <v>5.7835</v>
@@ -1546,13 +1546,13 @@
         <v>11.6841</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.7702</v>
+        <v>-2.8428</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.6236</v>
+        <v>-3.696299999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8536000000000002</v>
+        <v>0.8536999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-1.7801</v>
@@ -1561,7 +1561,7 @@
         <v>6.0022</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.7824</v>
+        <v>-7.782399999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.8176</v>
+        <v>4.4908</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3244</v>
+        <v>2.0253</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4933</v>
+        <v>2.4654</v>
       </c>
       <c r="G15" t="n">
         <v>1.6401</v>
@@ -1624,13 +1624,13 @@
         <v>2.1421</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7881</v>
+        <v>0.4612</v>
       </c>
       <c r="T15" t="n">
-        <v>0.09229999999999999</v>
+        <v>-0.2067</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6958</v>
+        <v>0.6679</v>
       </c>
       <c r="V15" t="n">
         <v>1.2211</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2624</v>
+        <v>2.9032</v>
       </c>
       <c r="E16" t="n">
-        <v>1.242</v>
+        <v>0.7436</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0204</v>
+        <v>2.1595</v>
       </c>
       <c r="G16" t="n">
         <v>0.7867</v>
@@ -1702,13 +1702,13 @@
         <v>1.9474</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5284</v>
+        <v>0.1691</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4015</v>
+        <v>-0.0969</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1269</v>
+        <v>0.266</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4616</v>
+        <v>2.7382</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8809</v>
+        <v>2.0802</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5808</v>
+        <v>0.658</v>
       </c>
       <c r="G17" t="n">
         <v>1.9121</v>
@@ -1780,13 +1780,13 @@
         <v>1.3632</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5748</v>
+        <v>0.8514</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.155</v>
+        <v>0.0443</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7298</v>
+        <v>0.8071</v>
       </c>
       <c r="V17" t="n">
         <v>0.5590000000000001</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.639</v>
+        <v>1.9542</v>
       </c>
       <c r="E18" t="n">
-        <v>0.246</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>1.393</v>
+        <v>1.3095</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1277</v>
@@ -1858,13 +1858,13 @@
         <v>1.3632</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4544</v>
+        <v>-0.1391</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.4052</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3495</v>
+        <v>0.266</v>
       </c>
       <c r="V18" t="n">
         <v>1.8316</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3707</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3321</v>
+        <v>0.4318</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0386</v>
+        <v>0.122</v>
       </c>
       <c r="G19" t="n">
         <v>-0.1913</v>
@@ -1936,13 +1936,13 @@
         <v>0.1947</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1917</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2473</v>
+        <v>-0.1477</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0557</v>
+        <v>0.1391</v>
       </c>
       <c r="V19" t="n">
         <v>0.5590000000000001</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H. GOMEZ GARCIA</t>
+          <t>A. MONRABAL ROMEU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2929</v>
+        <v>0.2694</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5776</v>
+        <v>-2.3012</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2847</v>
+        <v>2.5705</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4645</v>
+        <v>-0.9703000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2326</v>
+        <v>-0.7939000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2318</v>
+        <v>-0.1764</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1448</v>
+        <v>-1.2297</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5208</v>
+        <v>-0.5413</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.624</v>
+        <v>-0.6883</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3197</v>
+        <v>0.2594</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7118</v>
+        <v>-0.2526</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3921</v>
+        <v>0.5119</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3895</v>
+        <v>0.7789</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9737</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3632</v>
+        <v>1.7526</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4389</v>
+        <v>0.7402</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6802</v>
+        <v>-0.0978</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2412</v>
+        <v>0.838</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2211</v>
+        <v>-0.2795</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2211</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. MONRABAL ROMEU</t>
+          <t>H. GOMEZ GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4616</v>
+        <v>0.2171</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8992</v>
+        <v>-1.1789</v>
       </c>
       <c r="F21" t="n">
-        <v>2.4376</v>
+        <v>1.396</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9703000000000001</v>
+        <v>-1.4645</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7939000000000001</v>
+        <v>-1.2326</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1764</v>
+        <v>-0.2318</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2297</v>
+        <v>-1.1448</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5413</v>
+        <v>-0.5208</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6883</v>
+        <v>-0.624</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2594</v>
+        <v>-0.3197</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2526</v>
+        <v>-0.7118</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5119</v>
+        <v>0.3921</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7789</v>
+        <v>0.3895</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9737</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7526</v>
+        <v>1.3632</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0092</v>
+        <v>0.0711</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6959</v>
+        <v>-0.2815</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.3525</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2795</v>
+        <v>1.2211</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. GADEA HIERRO</t>
+          <t>J. RODENAS SANCHEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1453</v>
+        <v>-1.0024</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7681</v>
+        <v>-1.6179</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3771</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9517</v>
+        <v>0.1847</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3927</v>
+        <v>-1.1074</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5590000000000001</v>
+        <v>1.2921</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.6189</v>
+        <v>0.3175</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9467</v>
+        <v>-0.3232</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6722</v>
+        <v>0.6407</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3328</v>
+        <v>-0.1328</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.446</v>
+        <v>-0.7842</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1132</v>
+        <v>0.6514</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1947</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9737</v>
+        <v>-1.9474</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1684</v>
+        <v>1.3632</v>
       </c>
       <c r="S22" t="n">
-        <v>1.8327</v>
+        <v>0.6181</v>
       </c>
       <c r="T22" t="n">
-        <v>1.545</v>
+        <v>0.012</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2878</v>
+        <v>0.6061</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2211</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.5005</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. RODENAS SANCHEZ</t>
+          <t>J. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3949</v>
+        <v>-2.0631</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0166</v>
+        <v>-3.9868</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6217</v>
+        <v>1.9237</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1847</v>
+        <v>-2.4022</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1074</v>
+        <v>-0.8611</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2921</v>
+        <v>-1.5412</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3175</v>
+        <v>-2.9642</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3232</v>
+        <v>-0.898</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6407</v>
+        <v>-2.0662</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1328</v>
+        <v>0.5619</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7842</v>
+        <v>0.0369</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6514</v>
+        <v>0.525</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.5842000000000001</v>
+        <v>0.7789</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9474</v>
+        <v>-0.9737</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3632</v>
+        <v>1.7526</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2257</v>
+        <v>0.1707</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3867</v>
+        <v>-0.0489</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6123</v>
+        <v>0.2196</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2211</v>
+        <v>-0.6105</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2211</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. GOMEZ CARBONELL</t>
+          <t>A. GADEA HIERRO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.4766</v>
+        <v>-2.1644</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.289</v>
+        <v>-1.8646</v>
       </c>
       <c r="F24" t="n">
-        <v>1.8124</v>
+        <v>-0.2999</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.4022</v>
+        <v>-1.9517</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.8611</v>
+        <v>-1.3927</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.5412</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.9642</v>
+        <v>-1.6189</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.898</v>
+        <v>-0.9467</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.0662</v>
+        <v>-0.6722</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5619</v>
+        <v>-0.3328</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0369</v>
+        <v>-0.446</v>
       </c>
       <c r="O24" t="n">
-        <v>0.525</v>
+        <v>0.1132</v>
       </c>
       <c r="P24" t="n">
-        <v>0.7789</v>
+        <v>0.1947</v>
       </c>
       <c r="Q24" t="n">
         <v>-0.9737</v>
       </c>
       <c r="R24" t="n">
-        <v>1.7526</v>
+        <v>1.1684</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7572</v>
+        <v>0.8136</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6488</v>
+        <v>0.4486</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1083</v>
+        <v>0.365</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6105</v>
+        <v>-1.2211</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.6105</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.7039</v>
+        <v>-3.1561</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.2976</v>
+        <v>-4.7993</v>
       </c>
       <c r="F25" t="n">
-        <v>1.5938</v>
+        <v>1.6432</v>
       </c>
       <c r="G25" t="n">
         <v>-2.7845</v>
@@ -2404,13 +2404,13 @@
         <v>1.1684</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1391</v>
+        <v>0.6869</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5722</v>
+        <v>-0.0738</v>
       </c>
       <c r="U25" t="n">
-        <v>0.7113</v>
+        <v>0.7607</v>
       </c>
       <c r="V25" t="n">
         <v>-0.2795</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>4.076100000000001</v>
+        <v>4.7408</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.822700000000001</v>
+        <v>-9.8231</v>
       </c>
       <c r="F26" t="n">
-        <v>13.8992</v>
+        <v>14.5633</v>
       </c>
       <c r="G26" t="n">
         <v>-5.368600000000001</v>
@@ -2452,13 +2452,13 @@
         <v>-4.769699999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.599</v>
+        <v>-0.5990000000000001</v>
       </c>
       <c r="J26" t="n">
         <v>-5.067400000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.7165000000000001</v>
+        <v>0.7164999999999997</v>
       </c>
       <c r="L26" t="n">
         <v>-5.7837</v>
@@ -2482,13 +2482,13 @@
         <v>15.579</v>
       </c>
       <c r="S26" t="n">
-        <v>3.7702</v>
+        <v>4.4347</v>
       </c>
       <c r="T26" t="n">
         <v>-0.8535999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>4.623699999999999</v>
+        <v>5.288</v>
       </c>
       <c r="V26" t="n">
         <v>1.7801</v>
